--- a/Project.xlsx
+++ b/Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Testing\manual_testing_and_Agile\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FE5049-8682-4004-951E-861E8E0E2E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB66929-6E6F-44AD-A303-341FED58D422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{927D5387-D662-4A80-9A3D-5B60B79FE487}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{927D5387-D662-4A80-9A3D-5B60B79FE487}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Scenarios_Time" sheetId="2" r:id="rId1"/>
@@ -3106,6 +3106,153 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="3" tint="-0.249977111117893"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -3295,153 +3442,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="3" tint="-0.249977111117893"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3469,24 +3469,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F33395E0-4C8F-42C1-94E0-0EF5435542F4}" name="Table32" displayName="Table32" ref="B7:E1822" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowCellStyle="60% - Accent5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F33395E0-4C8F-42C1-94E0-0EF5435542F4}" name="Table32" displayName="Table32" ref="B7:E1822" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowCellStyle="60% - Accent5">
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{5744D7C0-B44A-4098-9257-969A4A944EAA}" name="TS_No." dataDxfId="8"/>
-    <tableColumn id="1" xr3:uid="{1B745E25-68AD-47CD-ACF7-E3B66875D703}" name="Test Scenario" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{B0D05148-1589-40F1-8E83-A88DC5122B4E}" name="Description " dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{4FE137AC-5D3F-4420-941E-25EE9B687323}" name="Expected Outcome" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{5744D7C0-B44A-4098-9257-969A4A944EAA}" name="TS_No." dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{1B745E25-68AD-47CD-ACF7-E3B66875D703}" name="Test Scenario" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{B0D05148-1589-40F1-8E83-A88DC5122B4E}" name="Description " dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{4FE137AC-5D3F-4420-941E-25EE9B687323}" name="Expected Outcome" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DFE9F097-52B5-419B-8612-042369D208A6}" name="Table3" displayName="Table3" ref="A6:D1815" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowCellStyle="60% - Accent5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DFE9F097-52B5-419B-8612-042369D208A6}" name="Table3" displayName="Table3" ref="A6:D1815" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowCellStyle="60% - Accent5">
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{BCAE70F1-99EC-42C7-8FB9-017F6A63757A}" name="TS_No." dataDxfId="14"/>
-    <tableColumn id="1" xr3:uid="{5BB7ADC7-5373-4DEE-9D33-3D671E75F43A}" name="Test Scenario" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{C077CD7D-14CC-4159-9250-921F6CBEF32D}" name="Description " dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{0B0E5E7A-D0A5-450E-90D9-0DAF9A64AF41}" name="Expected Result" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{BCAE70F1-99EC-42C7-8FB9-017F6A63757A}" name="TS_No." dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{5BB7ADC7-5373-4DEE-9D33-3D671E75F43A}" name="Test Scenario" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C077CD7D-14CC-4159-9250-921F6CBEF32D}" name="Description " dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{0B0E5E7A-D0A5-450E-90D9-0DAF9A64AF41}" name="Expected Result" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16668,19 +16668,19 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G1:H1 G3:H1048576 G2 I2">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="LOW">
+    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="VERY HIGH">
+    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="VERY HIGH">
       <formula>NOT(ISERROR(SEARCH("VERY HIGH",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="10" operator="containsText" text="HIGH">
+    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="VERY HIGH">
+    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="VERY HIGH">
       <formula>NOT(ISERROR(SEARCH("VERY HIGH",G1)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="12" operator="containsText" text="VERY HIGH">
@@ -16702,14 +16702,15 @@
   <dimension ref="B1:J28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" customWidth="1"/>
-    <col min="5" max="5" width="30.54296875" customWidth="1"/>
-    <col min="6" max="6" width="1.453125" customWidth="1"/>
-    <col min="7" max="7" width="30.90625" customWidth="1"/>
-    <col min="8" max="8" width="19.81640625" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -16764,7 +16765,7 @@
       <c r="H4" s="127"/>
       <c r="I4" s="127"/>
     </row>
-    <row r="5" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" ht="37" x14ac:dyDescent="0.35">
       <c r="B5" s="57" t="s">
         <v>4</v>
       </c>
@@ -16787,7 +16788,7 @@
       <c r="I6" s="126"/>
       <c r="J6" s="127"/>
     </row>
-    <row r="7" spans="2:10" ht="31" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10" ht="41" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="19" t="s">
         <v>1</v>
       </c>

--- a/Project.xlsx
+++ b/Project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Testing\manual_testing_and_Agile\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB66929-6E6F-44AD-A303-341FED58D422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBE9AB3-8A6C-4B1A-A2A6-8CA8FDB129AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{927D5387-D662-4A80-9A3D-5B60B79FE487}"/>
   </bookViews>
@@ -2414,7 +2414,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2711,9 +2711,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="23" xfId="3" applyBorder="1" applyAlignment="1">
@@ -3106,6 +3103,41 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6D6D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -3251,41 +3283,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6D6D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3481,12 +3478,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DFE9F097-52B5-419B-8612-042369D208A6}" name="Table3" displayName="Table3" ref="A6:D1815" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowCellStyle="60% - Accent5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DFE9F097-52B5-419B-8612-042369D208A6}" name="Table3" displayName="Table3" ref="A6:D1815" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowCellStyle="60% - Accent5">
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{BCAE70F1-99EC-42C7-8FB9-017F6A63757A}" name="TS_No." dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{5BB7ADC7-5373-4DEE-9D33-3D671E75F43A}" name="Test Scenario" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C077CD7D-14CC-4159-9250-921F6CBEF32D}" name="Description " dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{0B0E5E7A-D0A5-450E-90D9-0DAF9A64AF41}" name="Expected Result" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{BCAE70F1-99EC-42C7-8FB9-017F6A63757A}" name="TS_No." dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{5BB7ADC7-5373-4DEE-9D33-3D671E75F43A}" name="Test Scenario" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C077CD7D-14CC-4159-9250-921F6CBEF32D}" name="Description " dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{0B0E5E7A-D0A5-450E-90D9-0DAF9A64AF41}" name="Expected Result" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3864,7 +3861,7 @@
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="103" t="s">
         <v>100</v>
       </c>
       <c r="E8" s="7"/>
@@ -3940,7 +3937,7 @@
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="104" t="s">
         <v>101</v>
       </c>
       <c r="C16" s="63"/>
@@ -3961,7 +3958,7 @@
       <c r="B18" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="157" t="s">
+      <c r="C18" s="156" t="s">
         <v>112</v>
       </c>
       <c r="D18" s="43"/>
@@ -4018,7 +4015,7 @@
       <c r="E23" s="67"/>
     </row>
     <row r="24" spans="2:5" s="15" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="105" t="s">
+      <c r="B24" s="104" t="s">
         <v>105</v>
       </c>
       <c r="C24" s="68"/>
@@ -4076,7 +4073,7 @@
       <c r="E29" s="70"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="106" t="s">
+      <c r="B30" s="105" t="s">
         <v>106</v>
       </c>
       <c r="C30" s="72"/>
@@ -4094,7 +4091,7 @@
       <c r="E31" s="9"/>
     </row>
     <row r="32" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="106" t="s">
         <v>108</v>
       </c>
       <c r="C32" s="75"/>
@@ -14883,114 +14880,114 @@
   <dimension ref="B1:J43"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7265625" style="135" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" style="141" customWidth="1"/>
-    <col min="3" max="3" width="10" style="140" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" style="141" customWidth="1"/>
-    <col min="5" max="5" width="24.54296875" style="141" customWidth="1"/>
-    <col min="6" max="6" width="37.6328125" style="142" customWidth="1"/>
-    <col min="7" max="7" width="18.54296875" style="141" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" style="141" customWidth="1"/>
-    <col min="9" max="9" width="17.08984375" style="204" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" style="207"/>
-    <col min="11" max="16384" width="8.7265625" style="135"/>
+    <col min="1" max="1" width="2.7265625" style="134" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" style="140" customWidth="1"/>
+    <col min="3" max="3" width="10" style="139" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" style="140" customWidth="1"/>
+    <col min="5" max="5" width="24.54296875" style="140" customWidth="1"/>
+    <col min="6" max="6" width="37.6328125" style="141" customWidth="1"/>
+    <col min="7" max="7" width="18.54296875" style="140" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="140" customWidth="1"/>
+    <col min="9" max="9" width="17.08984375" style="203" customWidth="1"/>
+    <col min="10" max="10" width="8.7265625" style="206"/>
+    <col min="11" max="16384" width="8.7265625" style="134"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="234" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" s="167" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="168" t="s">
+    <row r="1" spans="2:10" s="233" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:10" s="166" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="169" t="s">
+      <c r="C2" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="170"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="172"/>
-    </row>
-    <row r="3" spans="2:10" s="167" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="173" t="s">
+      <c r="D2" s="169"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="171"/>
+    </row>
+    <row r="3" spans="2:10" s="166" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="174" t="s">
+      <c r="C3" s="173" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="175"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="176"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="206"/>
-    </row>
-    <row r="4" spans="2:10" s="167" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="177" t="s">
+      <c r="D3" s="174"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="205"/>
+    </row>
+    <row r="4" spans="2:10" s="166" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="176" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="178"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="179"/>
-      <c r="J4" s="180"/>
-    </row>
-    <row r="5" spans="2:10" s="167" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="186" t="s">
+      <c r="D4" s="177"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="179"/>
+    </row>
+    <row r="5" spans="2:10" s="166" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="185" t="s">
         <v>316</v>
       </c>
-      <c r="C5" s="174" t="s">
+      <c r="C5" s="173" t="s">
         <v>317</v>
       </c>
-      <c r="D5" s="181"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="206"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="175"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="205"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="158"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="139"/>
-    </row>
-    <row r="7" spans="2:10" s="167" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="164" t="s">
+      <c r="B6" s="157"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="138"/>
+    </row>
+    <row r="7" spans="2:10" s="166" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="165" t="s">
+      <c r="C7" s="164" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="164" t="s">
+      <c r="D7" s="163" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="164" t="s">
+      <c r="E7" s="163" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="164" t="s">
+      <c r="F7" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="165" t="s">
+      <c r="G7" s="164" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="165" t="s">
+      <c r="H7" s="164" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="165" t="s">
         <v>92</v>
       </c>
       <c r="J7" s="20" t="s">
@@ -14998,755 +14995,755 @@
       </c>
     </row>
     <row r="8" spans="2:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="163" t="s">
+      <c r="B8" s="162" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="2:10" s="156" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="143" t="s">
+    <row r="9" spans="2:10" s="155" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="142" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="159" t="s">
+      <c r="C9" s="158" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="160" t="s">
+      <c r="D9" s="159" t="s">
         <v>202</v>
       </c>
-      <c r="E9" s="160" t="s">
+      <c r="E9" s="159" t="s">
         <v>421</v>
       </c>
-      <c r="F9" s="209" t="s">
+      <c r="F9" s="208" t="s">
         <v>194</v>
       </c>
-      <c r="G9" s="143" t="s">
+      <c r="G9" s="142" t="s">
         <v>346</v>
       </c>
-      <c r="H9" s="143" t="s">
+      <c r="H9" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I9" s="143" t="s">
+      <c r="I9" s="142" t="s">
         <v>423</v>
       </c>
-      <c r="J9" s="208" t="s">
+      <c r="J9" s="207" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="52" x14ac:dyDescent="0.3">
-      <c r="B10" s="143" t="s">
+      <c r="B10" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="143" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="145" t="s">
+      <c r="D10" s="144" t="s">
         <v>203</v>
       </c>
-      <c r="E10" s="145" t="s">
+      <c r="E10" s="144" t="s">
         <v>199</v>
       </c>
-      <c r="F10" s="147" t="s">
+      <c r="F10" s="146" t="s">
         <v>195</v>
       </c>
-      <c r="G10" s="148"/>
-      <c r="H10" s="145" t="s">
+      <c r="G10" s="147"/>
+      <c r="H10" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="I10" s="204" t="s">
+      <c r="I10" s="203" t="s">
         <v>345</v>
       </c>
-      <c r="J10" s="207" t="s">
+      <c r="J10" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="52" x14ac:dyDescent="0.3">
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="143" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="145" t="s">
+      <c r="D11" s="144" t="s">
         <v>347</v>
       </c>
-      <c r="E11" s="145" t="s">
+      <c r="E11" s="144" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="147" t="s">
+      <c r="F11" s="146" t="s">
         <v>348</v>
       </c>
-      <c r="G11" s="148"/>
-      <c r="H11" s="145" t="s">
+      <c r="G11" s="147"/>
+      <c r="H11" s="144" t="s">
         <v>191</v>
       </c>
-      <c r="I11" s="204" t="s">
+      <c r="I11" s="203" t="s">
         <v>349</v>
       </c>
-      <c r="J11" s="207" t="s">
+      <c r="J11" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="52" x14ac:dyDescent="0.3">
-      <c r="B12" s="143" t="s">
+      <c r="B12" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="143" t="s">
         <v>185</v>
       </c>
-      <c r="D12" s="145" t="s">
+      <c r="D12" s="144" t="s">
         <v>205</v>
       </c>
-      <c r="E12" s="145" t="s">
+      <c r="E12" s="144" t="s">
         <v>199</v>
       </c>
-      <c r="F12" s="146" t="s">
+      <c r="F12" s="145" t="s">
         <v>201</v>
       </c>
-      <c r="H12" s="145" t="s">
+      <c r="H12" s="144" t="s">
         <v>350</v>
       </c>
-      <c r="I12" s="145" t="s">
+      <c r="I12" s="144" t="s">
         <v>351</v>
       </c>
-      <c r="J12" s="207" t="s">
+      <c r="J12" s="206" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="2:10" s="156" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="143" t="s">
+    <row r="13" spans="2:10" s="155" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="142" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="159" t="s">
+      <c r="C13" s="158" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="160" t="s">
+      <c r="D13" s="159" t="s">
         <v>354</v>
       </c>
-      <c r="E13" s="160" t="s">
+      <c r="E13" s="159" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="209" t="s">
+      <c r="F13" s="208" t="s">
         <v>355</v>
       </c>
-      <c r="G13" s="155"/>
-      <c r="H13" s="160" t="s">
+      <c r="G13" s="154"/>
+      <c r="H13" s="159" t="s">
         <v>212</v>
       </c>
-      <c r="I13" s="205" t="s">
+      <c r="I13" s="204" t="s">
         <v>356</v>
       </c>
-      <c r="J13" s="208" t="s">
+      <c r="J13" s="207" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="2:10" s="220" customFormat="1" ht="104" x14ac:dyDescent="0.3">
-      <c r="B14" s="221" t="s">
+    <row r="14" spans="2:10" s="219" customFormat="1" ht="104" x14ac:dyDescent="0.3">
+      <c r="B14" s="220" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="215" t="s">
+      <c r="C14" s="214" t="s">
         <v>192</v>
       </c>
-      <c r="D14" s="216" t="s">
+      <c r="D14" s="215" t="s">
         <v>361</v>
       </c>
-      <c r="E14" s="216" t="s">
+      <c r="E14" s="215" t="s">
         <v>422</v>
       </c>
-      <c r="F14" s="217" t="s">
+      <c r="F14" s="216" t="s">
         <v>362</v>
       </c>
-      <c r="G14" s="223"/>
-      <c r="H14" s="216" t="s">
+      <c r="G14" s="222"/>
+      <c r="H14" s="215" t="s">
         <v>211</v>
       </c>
-      <c r="I14" s="218" t="s">
+      <c r="I14" s="217" t="s">
         <v>353</v>
       </c>
-      <c r="J14" s="219" t="s">
+      <c r="J14" s="218" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="15" spans="2:10" s="156" customFormat="1" ht="78" x14ac:dyDescent="0.3">
-      <c r="B15" s="149" t="s">
+    <row r="15" spans="2:10" s="155" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+      <c r="B15" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="159" t="s">
+      <c r="C15" s="158" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="160" t="s">
+      <c r="D15" s="159" t="s">
         <v>367</v>
       </c>
-      <c r="E15" s="160" t="s">
+      <c r="E15" s="159" t="s">
         <v>365</v>
       </c>
-      <c r="F15" s="209" t="s">
+      <c r="F15" s="208" t="s">
         <v>366</v>
       </c>
-      <c r="G15" s="155"/>
-      <c r="H15" s="160" t="s">
+      <c r="G15" s="154"/>
+      <c r="H15" s="159" t="s">
         <v>368</v>
       </c>
-      <c r="I15" s="205" t="s">
+      <c r="I15" s="204" t="s">
         <v>369</v>
       </c>
-      <c r="J15" s="208" t="s">
+      <c r="J15" s="207" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="2:10" s="156" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="149" t="s">
+    <row r="16" spans="2:10" s="155" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="159" t="s">
+      <c r="C16" s="158" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="160" t="s">
+      <c r="D16" s="159" t="s">
         <v>357</v>
       </c>
-      <c r="E16" s="160" t="s">
+      <c r="E16" s="159" t="s">
         <v>193</v>
       </c>
-      <c r="F16" s="160" t="s">
+      <c r="F16" s="159" t="s">
         <v>358</v>
       </c>
-      <c r="G16" s="155"/>
-      <c r="H16" s="143" t="s">
+      <c r="G16" s="154"/>
+      <c r="H16" s="142" t="s">
         <v>310</v>
       </c>
-      <c r="I16" s="143" t="s">
+      <c r="I16" s="142" t="s">
         <v>359</v>
       </c>
-      <c r="J16" s="207" t="s">
+      <c r="J16" s="206" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="2:10" s="156" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="149" t="s">
+    <row r="17" spans="2:10" s="155" customFormat="1" ht="48.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="159" t="s">
+      <c r="C17" s="158" t="s">
         <v>210</v>
       </c>
-      <c r="D17" s="160" t="s">
+      <c r="D17" s="159" t="s">
         <v>313</v>
       </c>
-      <c r="E17" s="160" t="s">
+      <c r="E17" s="159" t="s">
         <v>214</v>
       </c>
-      <c r="F17" s="160" t="s">
+      <c r="F17" s="159" t="s">
         <v>215</v>
       </c>
-      <c r="G17" s="155"/>
-      <c r="H17" s="143" t="s">
+      <c r="G17" s="154"/>
+      <c r="H17" s="142" t="s">
         <v>311</v>
       </c>
-      <c r="I17" s="143" t="s">
+      <c r="I17" s="142" t="s">
         <v>360</v>
       </c>
-      <c r="J17" s="207" t="s">
+      <c r="J17" s="206" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="2:10" s="156" customFormat="1" ht="65" x14ac:dyDescent="0.3">
-      <c r="B18" s="149" t="s">
+    <row r="18" spans="2:10" s="155" customFormat="1" ht="65" x14ac:dyDescent="0.3">
+      <c r="B18" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="159" t="s">
+      <c r="C18" s="158" t="s">
         <v>210</v>
       </c>
-      <c r="D18" s="160" t="s">
+      <c r="D18" s="159" t="s">
         <v>314</v>
       </c>
-      <c r="E18" s="160" t="s">
+      <c r="E18" s="159" t="s">
         <v>214</v>
       </c>
-      <c r="F18" s="160" t="s">
+      <c r="F18" s="159" t="s">
         <v>315</v>
       </c>
-      <c r="G18" s="155"/>
-      <c r="H18" s="143" t="s">
+      <c r="G18" s="154"/>
+      <c r="H18" s="142" t="s">
         <v>311</v>
       </c>
-      <c r="I18" s="143" t="s">
+      <c r="I18" s="142" t="s">
         <v>360</v>
       </c>
-      <c r="J18" s="207" t="s">
+      <c r="J18" s="206" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="2:10" s="220" customFormat="1" ht="78" x14ac:dyDescent="0.3">
-      <c r="B19" s="221" t="s">
+    <row r="19" spans="2:10" s="219" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+      <c r="B19" s="220" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="215" t="s">
+      <c r="C19" s="214" t="s">
         <v>213</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="221" t="s">
         <v>251</v>
       </c>
-      <c r="E19" s="216" t="s">
+      <c r="E19" s="215" t="s">
         <v>309</v>
       </c>
-      <c r="F19" s="216" t="s">
+      <c r="F19" s="215" t="s">
         <v>209</v>
       </c>
-      <c r="G19" s="223"/>
-      <c r="H19" s="214" t="s">
+      <c r="G19" s="222"/>
+      <c r="H19" s="213" t="s">
         <v>312</v>
       </c>
-      <c r="I19" s="214" t="s">
+      <c r="I19" s="213" t="s">
         <v>364</v>
       </c>
-      <c r="J19" s="219" t="s">
+      <c r="J19" s="218" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="2:10" s="220" customFormat="1" ht="91" x14ac:dyDescent="0.3">
-      <c r="B20" s="221" t="s">
+    <row r="20" spans="2:10" s="219" customFormat="1" ht="91" x14ac:dyDescent="0.3">
+      <c r="B20" s="220" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="215" t="s">
+      <c r="C20" s="214" t="s">
         <v>219</v>
       </c>
-      <c r="D20" s="216" t="s">
+      <c r="D20" s="215" t="s">
         <v>216</v>
       </c>
-      <c r="E20" s="216" t="s">
+      <c r="E20" s="215" t="s">
         <v>217</v>
       </c>
-      <c r="F20" s="216" t="s">
+      <c r="F20" s="215" t="s">
         <v>230</v>
       </c>
-      <c r="G20" s="223"/>
-      <c r="H20" s="224" t="s">
+      <c r="G20" s="222"/>
+      <c r="H20" s="223" t="s">
         <v>343</v>
       </c>
-      <c r="I20" s="218" t="s">
+      <c r="I20" s="217" t="s">
         <v>363</v>
       </c>
-      <c r="J20" s="219" t="s">
+      <c r="J20" s="218" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B21" s="149" t="s">
+      <c r="B21" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="143" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="145" t="s">
+      <c r="D21" s="144" t="s">
         <v>221</v>
       </c>
-      <c r="E21" s="145" t="s">
+      <c r="E21" s="144" t="s">
         <v>217</v>
       </c>
-      <c r="F21" s="145" t="s">
+      <c r="F21" s="144" t="s">
         <v>223</v>
       </c>
-      <c r="H21" s="145" t="s">
+      <c r="H21" s="144" t="s">
         <v>224</v>
       </c>
-      <c r="I21" s="204" t="s">
+      <c r="I21" s="203" t="s">
         <v>370</v>
       </c>
-      <c r="J21" s="207" t="s">
+      <c r="J21" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B22" s="149" t="s">
+      <c r="B22" s="148" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="143" t="s">
         <v>227</v>
       </c>
-      <c r="D22" s="145" t="s">
+      <c r="D22" s="144" t="s">
         <v>373</v>
       </c>
-      <c r="E22" s="145" t="s">
+      <c r="E22" s="144" t="s">
         <v>374</v>
       </c>
-      <c r="F22" s="145" t="s">
+      <c r="F22" s="144" t="s">
         <v>223</v>
       </c>
-      <c r="H22" s="145" t="s">
+      <c r="H22" s="144" t="s">
         <v>375</v>
       </c>
-      <c r="I22" s="145" t="s">
+      <c r="I22" s="144" t="s">
         <v>376</v>
       </c>
-      <c r="J22" s="207" t="s">
+      <c r="J22" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B23" s="210" t="s">
+      <c r="B23" s="209" t="s">
         <v>218</v>
       </c>
-      <c r="C23" s="144" t="s">
+      <c r="C23" s="143" t="s">
         <v>228</v>
       </c>
-      <c r="D23" s="150" t="s">
+      <c r="D23" s="149" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="211" t="s">
+      <c r="E23" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="F23" s="211" t="s">
+      <c r="F23" s="210" t="s">
         <v>225</v>
       </c>
-      <c r="G23" s="212"/>
-      <c r="H23" s="211" t="s">
+      <c r="G23" s="211"/>
+      <c r="H23" s="210" t="s">
         <v>226</v>
       </c>
-      <c r="I23" s="211" t="s">
+      <c r="I23" s="210" t="s">
         <v>371</v>
       </c>
-      <c r="J23" s="213" t="s">
+      <c r="J23" s="212" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="2:10" s="156" customFormat="1" ht="93.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="149" t="s">
+    <row r="24" spans="2:10" s="155" customFormat="1" ht="93.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="C24" s="159" t="s">
+      <c r="C24" s="158" t="s">
         <v>237</v>
       </c>
-      <c r="D24" s="160" t="s">
+      <c r="D24" s="159" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="160" t="s">
+      <c r="E24" s="159" t="s">
         <v>232</v>
       </c>
-      <c r="F24" s="160" t="s">
+      <c r="F24" s="159" t="s">
         <v>233</v>
       </c>
-      <c r="G24" s="160" t="s">
+      <c r="G24" s="159" t="s">
         <v>234</v>
       </c>
-      <c r="H24" s="160" t="s">
+      <c r="H24" s="159" t="s">
         <v>235</v>
       </c>
-      <c r="I24" s="205"/>
-      <c r="J24" s="207" t="s">
+      <c r="I24" s="204"/>
+      <c r="J24" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="31" x14ac:dyDescent="0.3">
-      <c r="B25" s="163" t="s">
+      <c r="B25" s="162" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="151" t="s">
+      <c r="B26" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="143" t="s">
         <v>242</v>
       </c>
-      <c r="D26" s="145" t="s">
+      <c r="D26" s="144" t="s">
         <v>241</v>
       </c>
-      <c r="E26" s="145" t="s">
+      <c r="E26" s="144" t="s">
         <v>238</v>
       </c>
-      <c r="F26" s="145" t="s">
+      <c r="F26" s="144" t="s">
         <v>239</v>
       </c>
-      <c r="H26" s="145" t="s">
+      <c r="H26" s="144" t="s">
         <v>240</v>
       </c>
-      <c r="I26" s="145" t="s">
+      <c r="I26" s="144" t="s">
         <v>377</v>
       </c>
-      <c r="J26" s="207" t="s">
+      <c r="J26" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B27" s="151" t="s">
+      <c r="B27" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="143" t="s">
         <v>247</v>
       </c>
-      <c r="D27" s="145" t="s">
+      <c r="D27" s="144" t="s">
         <v>243</v>
       </c>
-      <c r="E27" s="142" t="s">
+      <c r="E27" s="141" t="s">
         <v>244</v>
       </c>
-      <c r="F27" s="142" t="s">
+      <c r="F27" s="141" t="s">
         <v>245</v>
       </c>
-      <c r="H27" s="147" t="s">
+      <c r="H27" s="146" t="s">
         <v>246</v>
       </c>
-      <c r="I27" s="204" t="s">
+      <c r="I27" s="203" t="s">
         <v>378</v>
       </c>
-      <c r="J27" s="207" t="s">
+      <c r="J27" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B28" s="147" t="s">
+      <c r="B28" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="143" t="s">
         <v>255</v>
       </c>
-      <c r="D28" s="145" t="s">
+      <c r="D28" s="144" t="s">
         <v>252</v>
       </c>
-      <c r="E28" s="145" t="s">
+      <c r="E28" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="F28" s="145" t="s">
+      <c r="F28" s="144" t="s">
         <v>277</v>
       </c>
-      <c r="G28" s="145" t="s">
+      <c r="G28" s="144" t="s">
         <v>253</v>
       </c>
-      <c r="H28" s="145" t="s">
+      <c r="H28" s="144" t="s">
         <v>254</v>
       </c>
-      <c r="I28" s="204" t="s">
+      <c r="I28" s="203" t="s">
         <v>379</v>
       </c>
-      <c r="J28" s="207" t="s">
+      <c r="J28" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="104" x14ac:dyDescent="0.3">
-      <c r="B29" s="147" t="s">
+      <c r="B29" s="146" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="143" t="s">
         <v>256</v>
       </c>
-      <c r="D29" s="147" t="s">
+      <c r="D29" s="146" t="s">
         <v>257</v>
       </c>
-      <c r="E29" s="145" t="s">
+      <c r="E29" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="145" t="s">
+      <c r="F29" s="144" t="s">
         <v>259</v>
       </c>
-      <c r="H29" s="147" t="s">
+      <c r="H29" s="146" t="s">
         <v>258</v>
       </c>
-      <c r="I29" s="147" t="s">
+      <c r="I29" s="146" t="s">
         <v>380</v>
       </c>
-      <c r="J29" s="207" t="s">
+      <c r="J29" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="91" x14ac:dyDescent="0.3">
-      <c r="B30" s="151" t="s">
+      <c r="B30" s="150" t="s">
         <v>250</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="143" t="s">
         <v>261</v>
       </c>
-      <c r="D30" s="145" t="s">
+      <c r="D30" s="144" t="s">
         <v>340</v>
       </c>
-      <c r="E30" s="145" t="s">
+      <c r="E30" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="F30" s="145" t="s">
+      <c r="F30" s="144" t="s">
         <v>262</v>
       </c>
-      <c r="H30" s="147" t="s">
+      <c r="H30" s="146" t="s">
         <v>260</v>
       </c>
-      <c r="I30" s="147" t="s">
+      <c r="I30" s="146" t="s">
         <v>381</v>
       </c>
-      <c r="J30" s="207" t="s">
+      <c r="J30" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="31" x14ac:dyDescent="0.3">
-      <c r="B31" s="163" t="s">
+      <c r="B31" s="162" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B32" s="147" t="s">
+      <c r="B32" s="146" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="143" t="s">
         <v>264</v>
       </c>
-      <c r="D32" s="147" t="s">
+      <c r="D32" s="146" t="s">
         <v>271</v>
       </c>
-      <c r="E32" s="147" t="s">
+      <c r="E32" s="146" t="s">
         <v>265</v>
       </c>
-      <c r="F32" s="147" t="s">
+      <c r="F32" s="146" t="s">
         <v>267</v>
       </c>
-      <c r="G32" s="147" t="s">
+      <c r="G32" s="146" t="s">
         <v>266</v>
       </c>
-      <c r="H32" s="147" t="s">
+      <c r="H32" s="146" t="s">
         <v>268</v>
       </c>
-      <c r="I32" s="147" t="s">
+      <c r="I32" s="146" t="s">
         <v>382</v>
       </c>
-      <c r="J32" s="207" t="s">
+      <c r="J32" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="65" x14ac:dyDescent="0.3">
-      <c r="B33" s="147" t="s">
+      <c r="B33" s="146" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="144" t="s">
+      <c r="C33" s="143" t="s">
         <v>278</v>
       </c>
-      <c r="D33" s="147" t="s">
+      <c r="D33" s="146" t="s">
         <v>384</v>
       </c>
-      <c r="E33" s="147" t="s">
+      <c r="E33" s="146" t="s">
         <v>269</v>
       </c>
-      <c r="F33" s="147" t="s">
+      <c r="F33" s="146" t="s">
         <v>270</v>
       </c>
-      <c r="G33" s="147" t="s">
+      <c r="G33" s="146" t="s">
         <v>385</v>
       </c>
-      <c r="H33" s="147" t="s">
+      <c r="H33" s="146" t="s">
         <v>383</v>
       </c>
-      <c r="I33" s="147" t="s">
+      <c r="I33" s="146" t="s">
         <v>386</v>
       </c>
-      <c r="J33" s="207" t="s">
+      <c r="J33" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B34" s="163" t="s">
+      <c r="B34" s="162" t="s">
         <v>180</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="161"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="162"/>
-      <c r="G34" s="161"/>
-      <c r="H34" s="161"/>
+      <c r="C34" s="143"/>
+      <c r="D34" s="160"/>
+      <c r="E34" s="160"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="160"/>
       <c r="I34" s="70"/>
     </row>
     <row r="35" spans="2:10" ht="65" x14ac:dyDescent="0.3">
-      <c r="B35" s="147" t="s">
+      <c r="B35" s="146" t="s">
         <v>274</v>
       </c>
-      <c r="C35" s="144" t="s">
+      <c r="C35" s="143" t="s">
         <v>281</v>
       </c>
-      <c r="D35" s="147" t="s">
+      <c r="D35" s="146" t="s">
         <v>275</v>
       </c>
-      <c r="E35" s="147" t="s">
+      <c r="E35" s="146" t="s">
         <v>276</v>
       </c>
-      <c r="F35" s="147" t="s">
+      <c r="F35" s="146" t="s">
         <v>388</v>
       </c>
-      <c r="G35" s="145" t="s">
+      <c r="G35" s="144" t="s">
         <v>395</v>
       </c>
-      <c r="H35" s="147" t="s">
+      <c r="H35" s="146" t="s">
         <v>396</v>
       </c>
-      <c r="I35" s="147" t="s">
+      <c r="I35" s="146" t="s">
         <v>397</v>
       </c>
-      <c r="J35" s="207" t="s">
+      <c r="J35" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="65" x14ac:dyDescent="0.3">
-      <c r="B36" s="154" t="s">
+      <c r="B36" s="153" t="s">
         <v>391</v>
       </c>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="143" t="s">
         <v>282</v>
       </c>
-      <c r="D36" s="147" t="s">
+      <c r="D36" s="146" t="s">
         <v>392</v>
       </c>
-      <c r="E36" s="147" t="s">
+      <c r="E36" s="146" t="s">
         <v>393</v>
       </c>
-      <c r="F36" s="147" t="s">
+      <c r="F36" s="146" t="s">
         <v>394</v>
       </c>
-      <c r="G36" s="145" t="s">
+      <c r="G36" s="144" t="s">
         <v>398</v>
       </c>
-      <c r="H36" s="147" t="s">
+      <c r="H36" s="146" t="s">
         <v>399</v>
       </c>
-      <c r="I36" s="147" t="s">
+      <c r="I36" s="146" t="s">
         <v>400</v>
       </c>
-      <c r="J36" s="207" t="s">
+      <c r="J36" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="65" x14ac:dyDescent="0.3">
-      <c r="B37" s="154" t="s">
+      <c r="B37" s="153" t="s">
         <v>280</v>
       </c>
-      <c r="C37" s="144" t="s">
+      <c r="C37" s="143" t="s">
         <v>282</v>
       </c>
-      <c r="D37" s="147" t="s">
+      <c r="D37" s="146" t="s">
         <v>279</v>
       </c>
-      <c r="E37" s="147" t="s">
+      <c r="E37" s="146" t="s">
         <v>276</v>
       </c>
-      <c r="F37" s="147" t="s">
+      <c r="F37" s="146" t="s">
         <v>389</v>
       </c>
-      <c r="H37" s="147" t="s">
+      <c r="H37" s="146" t="s">
         <v>401</v>
       </c>
-      <c r="I37" s="147" t="s">
+      <c r="I37" s="146" t="s">
         <v>402</v>
       </c>
-      <c r="J37" s="207" t="s">
+      <c r="J37" s="206" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="65" x14ac:dyDescent="0.3">
-      <c r="B38" s="152" t="s">
+      <c r="B38" s="151" t="s">
         <v>283</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="143" t="s">
         <v>284</v>
       </c>
-      <c r="D38" s="147" t="s">
+      <c r="D38" s="146" t="s">
         <v>292</v>
       </c>
-      <c r="E38" s="147" t="s">
+      <c r="E38" s="146" t="s">
         <v>289</v>
       </c>
-      <c r="F38" s="147" t="s">
+      <c r="F38" s="146" t="s">
         <v>290</v>
       </c>
-      <c r="H38" s="147" t="s">
+      <c r="H38" s="146" t="s">
         <v>291</v>
       </c>
       <c r="J38" s="4" t="s">
@@ -15754,22 +15751,22 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="152" t="s">
+      <c r="B39" s="151" t="s">
         <v>283</v>
       </c>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="143" t="s">
         <v>285</v>
       </c>
-      <c r="D39" s="147" t="s">
+      <c r="D39" s="146" t="s">
         <v>293</v>
       </c>
-      <c r="E39" s="147" t="s">
+      <c r="E39" s="146" t="s">
         <v>289</v>
       </c>
-      <c r="F39" s="147" t="s">
+      <c r="F39" s="146" t="s">
         <v>294</v>
       </c>
-      <c r="H39" s="147" t="s">
+      <c r="H39" s="146" t="s">
         <v>295</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -15777,76 +15774,76 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="78" x14ac:dyDescent="0.3">
-      <c r="B40" s="147" t="s">
+      <c r="B40" s="146" t="s">
         <v>273</v>
       </c>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="143" t="s">
         <v>287</v>
       </c>
-      <c r="D40" s="147" t="s">
+      <c r="D40" s="146" t="s">
         <v>297</v>
       </c>
-      <c r="E40" s="147" t="s">
+      <c r="E40" s="146" t="s">
         <v>289</v>
       </c>
-      <c r="F40" s="147" t="s">
+      <c r="F40" s="146" t="s">
         <v>296</v>
       </c>
-      <c r="H40" s="147" t="s">
+      <c r="H40" s="146" t="s">
         <v>298</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="41" spans="2:10" s="156" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="143" t="s">
+    <row r="41" spans="2:10" s="155" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="142" t="s">
         <v>286</v>
       </c>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="143" t="s">
         <v>288</v>
       </c>
-      <c r="D41" s="143" t="s">
+      <c r="D41" s="142" t="s">
         <v>307</v>
       </c>
-      <c r="E41" s="143" t="s">
+      <c r="E41" s="142" t="s">
         <v>289</v>
       </c>
-      <c r="F41" s="143" t="s">
+      <c r="F41" s="142" t="s">
         <v>390</v>
       </c>
-      <c r="G41" s="155"/>
-      <c r="H41" s="143" t="s">
+      <c r="G41" s="154"/>
+      <c r="H41" s="142" t="s">
         <v>308</v>
       </c>
-      <c r="I41" s="143" t="s">
+      <c r="I41" s="142" t="s">
         <v>404</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="42" spans="2:10" s="156" customFormat="1" ht="78" x14ac:dyDescent="0.3">
-      <c r="B42" s="143" t="s">
+    <row r="42" spans="2:10" s="155" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+      <c r="B42" s="142" t="s">
         <v>98</v>
       </c>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="143" t="s">
         <v>299</v>
       </c>
-      <c r="D42" s="143" t="s">
+      <c r="D42" s="142" t="s">
         <v>300</v>
       </c>
-      <c r="E42" s="147" t="s">
+      <c r="E42" s="146" t="s">
         <v>301</v>
       </c>
-      <c r="F42" s="147" t="s">
+      <c r="F42" s="146" t="s">
         <v>302</v>
       </c>
-      <c r="G42" s="155"/>
-      <c r="H42" s="143" t="s">
+      <c r="G42" s="154"/>
+      <c r="H42" s="142" t="s">
         <v>306</v>
       </c>
-      <c r="I42" s="143" t="s">
+      <c r="I42" s="142" t="s">
         <v>405</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -15854,25 +15851,25 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="56.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="147" t="s">
+      <c r="B43" s="146" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="144" t="s">
+      <c r="C43" s="143" t="s">
         <v>387</v>
       </c>
-      <c r="D43" s="147" t="s">
+      <c r="D43" s="146" t="s">
         <v>303</v>
       </c>
-      <c r="E43" s="147" t="s">
+      <c r="E43" s="146" t="s">
         <v>289</v>
       </c>
-      <c r="F43" s="147" t="s">
+      <c r="F43" s="146" t="s">
         <v>304</v>
       </c>
-      <c r="H43" s="147" t="s">
+      <c r="H43" s="146" t="s">
         <v>305</v>
       </c>
-      <c r="I43" s="147" t="s">
+      <c r="I43" s="146" t="s">
         <v>406</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -15902,622 +15899,622 @@
   <dimension ref="B1:I38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="183"/>
-    <col min="2" max="2" width="7.08984375" style="183" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" style="183" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="183" customWidth="1"/>
-    <col min="5" max="5" width="28.81640625" style="183" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="182"/>
+    <col min="2" max="2" width="7.08984375" style="182" customWidth="1"/>
+    <col min="3" max="3" width="24.90625" style="182" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="182" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" style="182" customWidth="1"/>
     <col min="6" max="6" width="30.6328125" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="183"/>
+    <col min="7" max="16384" width="8.7265625" style="182"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B1" s="235" t="s">
+      <c r="B1" s="234" t="s">
         <v>318</v>
       </c>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
     </row>
     <row r="2" spans="2:9" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-    </row>
-    <row r="3" spans="2:9" s="185" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="188" t="s">
+      <c r="B2" s="183"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="186"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+    </row>
+    <row r="3" spans="2:9" s="184" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="187" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="188" t="s">
+      <c r="C3" s="187" t="s">
         <v>320</v>
       </c>
-      <c r="D3" s="188" t="s">
+      <c r="D3" s="187" t="s">
         <v>321</v>
       </c>
-      <c r="E3" s="188" t="s">
+      <c r="E3" s="187" t="s">
         <v>322</v>
       </c>
-      <c r="F3" s="189" t="s">
+      <c r="F3" s="188" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B4" s="190">
+      <c r="B4" s="189">
         <v>3</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="189" t="s">
         <v>325</v>
       </c>
-      <c r="D4" s="190" t="s">
+      <c r="D4" s="189" t="s">
         <v>326</v>
       </c>
-      <c r="E4" s="191" t="s">
+      <c r="E4" s="190" t="s">
         <v>328</v>
       </c>
-      <c r="F4" s="191" t="s">
+      <c r="F4" s="190" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="190">
+      <c r="B5" s="189">
         <v>7</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="191" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="191"/>
+      <c r="D5" s="187"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="190"/>
     </row>
     <row r="6" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B6" s="190">
+      <c r="B6" s="189">
         <v>7</v>
       </c>
-      <c r="C6" s="193" t="s">
+      <c r="C6" s="192" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="190" t="s">
+      <c r="D6" s="189" t="s">
         <v>181</v>
       </c>
       <c r="E6" s="71" t="s">
         <v>202</v>
       </c>
-      <c r="F6" s="191" t="s">
+      <c r="F6" s="190" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B7" s="190">
+      <c r="B7" s="189">
         <v>7</v>
       </c>
-      <c r="C7" s="193" t="s">
+      <c r="C7" s="192" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="190" t="s">
+      <c r="D7" s="189" t="s">
         <v>183</v>
       </c>
       <c r="E7" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="F7" s="191" t="s">
+      <c r="F7" s="190" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B8" s="190">
+      <c r="B8" s="189">
         <v>7</v>
       </c>
-      <c r="C8" s="193" t="s">
+      <c r="C8" s="192" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="190" t="s">
+      <c r="D8" s="189" t="s">
         <v>184</v>
       </c>
       <c r="E8" s="71" t="s">
         <v>204</v>
       </c>
-      <c r="F8" s="191" t="s">
+      <c r="F8" s="190" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B9" s="190">
+      <c r="B9" s="189">
         <v>7</v>
       </c>
-      <c r="C9" s="193" t="s">
+      <c r="C9" s="192" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="190" t="s">
+      <c r="D9" s="189" t="s">
         <v>185</v>
       </c>
       <c r="E9" s="71" t="s">
         <v>205</v>
       </c>
-      <c r="F9" s="191" t="s">
+      <c r="F9" s="190" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B10" s="190">
+      <c r="B10" s="189">
         <v>7</v>
       </c>
-      <c r="C10" s="193" t="s">
+      <c r="C10" s="192" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="190" t="s">
+      <c r="D10" s="189" t="s">
         <v>186</v>
       </c>
       <c r="E10" s="71" t="s">
         <v>206</v>
       </c>
-      <c r="F10" s="191" t="s">
+      <c r="F10" s="190" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="190">
+      <c r="B11" s="189">
         <v>7</v>
       </c>
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="193" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="190" t="s">
+      <c r="D11" s="189" t="s">
         <v>192</v>
       </c>
       <c r="E11" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="F11" s="191" t="s">
+      <c r="F11" s="190" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="190">
+      <c r="B12" s="189">
         <v>7</v>
       </c>
-      <c r="C12" s="194" t="s">
+      <c r="C12" s="193" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="195" t="s">
+      <c r="D12" s="194" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="196" t="s">
+      <c r="E12" s="195" t="s">
         <v>208</v>
       </c>
-      <c r="F12" s="191" t="s">
+      <c r="F12" s="190" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B13" s="190">
+      <c r="B13" s="189">
         <v>7</v>
       </c>
-      <c r="C13" s="194" t="s">
+      <c r="C13" s="193" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="195" t="s">
+      <c r="D13" s="194" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="196" t="s">
+      <c r="E13" s="195" t="s">
         <v>313</v>
       </c>
-      <c r="F13" s="191" t="s">
+      <c r="F13" s="190" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="B14" s="190">
+      <c r="B14" s="189">
         <v>7</v>
       </c>
-      <c r="C14" s="194" t="s">
+      <c r="C14" s="193" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="195" t="s">
+      <c r="D14" s="194" t="s">
         <v>210</v>
       </c>
-      <c r="E14" s="196" t="s">
+      <c r="E14" s="195" t="s">
         <v>314</v>
       </c>
-      <c r="F14" s="191" t="s">
+      <c r="F14" s="190" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="190">
+      <c r="B15" s="189">
         <v>7</v>
       </c>
-      <c r="C15" s="194" t="s">
+      <c r="C15" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="190" t="s">
+      <c r="D15" s="189" t="s">
         <v>213</v>
       </c>
       <c r="E15" s="71" t="s">
         <v>251</v>
       </c>
-      <c r="F15" s="191" t="s">
+      <c r="F15" s="190" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="190">
+      <c r="B16" s="189">
         <v>7</v>
       </c>
-      <c r="C16" s="194" t="s">
+      <c r="C16" s="193" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="190" t="s">
+      <c r="D16" s="189" t="s">
         <v>219</v>
       </c>
       <c r="E16" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="F16" s="191" t="s">
+      <c r="F16" s="190" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B17" s="190">
+      <c r="B17" s="189">
         <v>7</v>
       </c>
-      <c r="C17" s="194" t="s">
+      <c r="C17" s="193" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="190" t="s">
+      <c r="D17" s="189" t="s">
         <v>220</v>
       </c>
       <c r="E17" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="191" t="s">
+      <c r="F17" s="190" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="190">
+      <c r="B18" s="189">
         <v>7</v>
       </c>
-      <c r="C18" s="194" t="s">
+      <c r="C18" s="193" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="190" t="s">
+      <c r="D18" s="189" t="s">
         <v>227</v>
       </c>
       <c r="E18" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="F18" s="191" t="s">
+      <c r="F18" s="190" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B19" s="190">
+      <c r="B19" s="189">
         <v>7</v>
       </c>
-      <c r="C19" s="194" t="s">
+      <c r="C19" s="193" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="195" t="s">
+      <c r="D19" s="194" t="s">
         <v>228</v>
       </c>
-      <c r="E19" s="196" t="s">
+      <c r="E19" s="195" t="s">
         <v>231</v>
       </c>
-      <c r="F19" s="191" t="s">
+      <c r="F19" s="190" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="190">
+      <c r="B20" s="189">
         <v>7</v>
       </c>
-      <c r="C20" s="163" t="s">
+      <c r="C20" s="162" t="s">
         <v>236</v>
       </c>
-      <c r="D20" s="197"/>
-      <c r="E20" s="197"/>
-      <c r="F20" s="191"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="190"/>
     </row>
     <row r="21" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B21" s="190">
+      <c r="B21" s="189">
         <v>7</v>
       </c>
-      <c r="C21" s="198" t="s">
+      <c r="C21" s="197" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="190" t="s">
+      <c r="D21" s="189" t="s">
         <v>237</v>
       </c>
       <c r="E21" s="71" t="s">
         <v>342</v>
       </c>
-      <c r="F21" s="191" t="s">
+      <c r="F21" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B22" s="190">
+      <c r="B22" s="189">
         <v>7</v>
       </c>
-      <c r="C22" s="198" t="s">
+      <c r="C22" s="197" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="190" t="s">
+      <c r="D22" s="189" t="s">
         <v>242</v>
       </c>
       <c r="E22" s="71" t="s">
         <v>243</v>
       </c>
-      <c r="F22" s="191" t="s">
+      <c r="F22" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="190">
+      <c r="B23" s="189">
         <v>7</v>
       </c>
-      <c r="C23" s="191" t="s">
+      <c r="C23" s="190" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="189" t="s">
         <v>247</v>
       </c>
       <c r="E23" s="71" t="s">
         <v>252</v>
       </c>
-      <c r="F23" s="191" t="s">
+      <c r="F23" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="190">
+      <c r="B24" s="189">
         <v>7</v>
       </c>
-      <c r="C24" s="191" t="s">
+      <c r="C24" s="190" t="s">
         <v>332</v>
       </c>
-      <c r="D24" s="190" t="s">
+      <c r="D24" s="189" t="s">
         <v>255</v>
       </c>
-      <c r="E24" s="199" t="s">
+      <c r="E24" s="198" t="s">
         <v>257</v>
       </c>
-      <c r="F24" s="191" t="s">
+      <c r="F24" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="B25" s="190">
+      <c r="B25" s="189">
         <v>7</v>
       </c>
-      <c r="C25" s="198" t="s">
+      <c r="C25" s="197" t="s">
         <v>250</v>
       </c>
-      <c r="D25" s="190" t="s">
+      <c r="D25" s="189" t="s">
         <v>256</v>
       </c>
       <c r="E25" s="71" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="191" t="s">
+      <c r="F25" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B26" s="190">
+      <c r="B26" s="189">
         <v>7</v>
       </c>
-      <c r="C26" s="163" t="s">
+      <c r="C26" s="162" t="s">
         <v>263</v>
       </c>
-      <c r="D26" s="197"/>
-      <c r="E26" s="197"/>
-      <c r="F26" s="191"/>
+      <c r="D26" s="196"/>
+      <c r="E26" s="196"/>
+      <c r="F26" s="190"/>
     </row>
     <row r="27" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B27" s="190">
+      <c r="B27" s="189">
         <v>7</v>
       </c>
-      <c r="C27" s="191" t="s">
+      <c r="C27" s="190" t="s">
         <v>103</v>
       </c>
-      <c r="D27" s="190" t="s">
+      <c r="D27" s="189" t="s">
         <v>261</v>
       </c>
-      <c r="E27" s="199" t="s">
+      <c r="E27" s="198" t="s">
         <v>271</v>
       </c>
-      <c r="F27" s="191" t="s">
+      <c r="F27" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B28" s="190">
+      <c r="B28" s="189">
         <v>7</v>
       </c>
-      <c r="C28" s="191" t="s">
+      <c r="C28" s="190" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="190" t="s">
+      <c r="D28" s="189" t="s">
         <v>264</v>
       </c>
-      <c r="E28" s="199" t="s">
+      <c r="E28" s="198" t="s">
         <v>272</v>
       </c>
-      <c r="F28" s="191" t="s">
+      <c r="F28" s="190" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B29" s="190">
+      <c r="B29" s="189">
         <v>7</v>
       </c>
-      <c r="C29" s="163" t="s">
+      <c r="C29" s="162" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="200"/>
-      <c r="E29" s="200"/>
-      <c r="F29" s="191"/>
+      <c r="D29" s="199"/>
+      <c r="E29" s="199"/>
+      <c r="F29" s="190"/>
     </row>
     <row r="30" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B30" s="190">
+      <c r="B30" s="189">
         <v>7</v>
       </c>
-      <c r="C30" s="191" t="s">
+      <c r="C30" s="190" t="s">
         <v>274</v>
       </c>
-      <c r="D30" s="190" t="s">
+      <c r="D30" s="189" t="s">
         <v>278</v>
       </c>
-      <c r="E30" s="199" t="s">
+      <c r="E30" s="198" t="s">
         <v>275</v>
       </c>
-      <c r="F30" s="191" t="s">
+      <c r="F30" s="190" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B31" s="190">
+      <c r="B31" s="189">
         <v>7</v>
       </c>
-      <c r="C31" s="191" t="s">
+      <c r="C31" s="190" t="s">
         <v>280</v>
       </c>
-      <c r="D31" s="190" t="s">
+      <c r="D31" s="189" t="s">
         <v>281</v>
       </c>
-      <c r="E31" s="199" t="s">
+      <c r="E31" s="198" t="s">
         <v>279</v>
       </c>
-      <c r="F31" s="191" t="s">
+      <c r="F31" s="190" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="190">
+      <c r="B32" s="189">
         <v>7</v>
       </c>
-      <c r="C32" s="190" t="s">
+      <c r="C32" s="189" t="s">
         <v>283</v>
       </c>
-      <c r="D32" s="190" t="s">
+      <c r="D32" s="189" t="s">
         <v>282</v>
       </c>
-      <c r="E32" s="199" t="s">
+      <c r="E32" s="198" t="s">
         <v>292</v>
       </c>
-      <c r="F32" s="191" t="s">
+      <c r="F32" s="190" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B33" s="190">
+      <c r="B33" s="189">
         <v>7</v>
       </c>
-      <c r="C33" s="190" t="s">
+      <c r="C33" s="189" t="s">
         <v>283</v>
       </c>
-      <c r="D33" s="190" t="s">
+      <c r="D33" s="189" t="s">
         <v>284</v>
       </c>
-      <c r="E33" s="199" t="s">
+      <c r="E33" s="198" t="s">
         <v>293</v>
       </c>
-      <c r="F33" s="191" t="s">
+      <c r="F33" s="190" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="B34" s="190">
+      <c r="B34" s="189">
         <v>7</v>
       </c>
-      <c r="C34" s="191" t="s">
+      <c r="C34" s="190" t="s">
         <v>273</v>
       </c>
-      <c r="D34" s="190" t="s">
+      <c r="D34" s="189" t="s">
         <v>285</v>
       </c>
-      <c r="E34" s="199" t="s">
+      <c r="E34" s="198" t="s">
         <v>297</v>
       </c>
-      <c r="F34" s="191" t="s">
+      <c r="F34" s="190" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B35" s="190">
+      <c r="B35" s="189">
         <v>7</v>
       </c>
-      <c r="C35" s="193" t="s">
+      <c r="C35" s="192" t="s">
         <v>286</v>
       </c>
-      <c r="D35" s="195" t="s">
+      <c r="D35" s="194" t="s">
         <v>287</v>
       </c>
-      <c r="E35" s="201" t="s">
+      <c r="E35" s="200" t="s">
         <v>307</v>
       </c>
-      <c r="F35" s="191" t="s">
+      <c r="F35" s="190" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="B36" s="190">
+      <c r="B36" s="189">
         <v>7</v>
       </c>
-      <c r="C36" s="193" t="s">
+      <c r="C36" s="192" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="190" t="s">
+      <c r="D36" s="189" t="s">
         <v>288</v>
       </c>
-      <c r="E36" s="201" t="s">
+      <c r="E36" s="200" t="s">
         <v>300</v>
       </c>
-      <c r="F36" s="191" t="s">
+      <c r="F36" s="190" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B37" s="190">
+      <c r="B37" s="189">
         <v>7</v>
       </c>
-      <c r="C37" s="191" t="s">
+      <c r="C37" s="190" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="190" t="s">
+      <c r="D37" s="189" t="s">
         <v>299</v>
       </c>
-      <c r="E37" s="199" t="s">
+      <c r="E37" s="198" t="s">
         <v>303</v>
       </c>
-      <c r="F37" s="191" t="s">
+      <c r="F37" s="190" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="B38" s="190">
+      <c r="B38" s="189">
         <v>3</v>
       </c>
-      <c r="C38" s="202" t="s">
+      <c r="C38" s="201" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="203" t="s">
+      <c r="D38" s="202" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="191" t="s">
+      <c r="E38" s="190" t="s">
         <v>336</v>
       </c>
-      <c r="F38" s="191" t="s">
+      <c r="F38" s="190" t="s">
         <v>337</v>
       </c>
     </row>
@@ -16535,130 +16532,130 @@
   <dimension ref="B1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="225"/>
-    <col min="2" max="2" width="11.6328125" style="225" customWidth="1"/>
-    <col min="3" max="3" width="18.36328125" style="225" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.54296875" style="225" customWidth="1"/>
-    <col min="5" max="5" width="26" style="225" customWidth="1"/>
-    <col min="6" max="6" width="23.90625" style="225" customWidth="1"/>
-    <col min="7" max="8" width="9.36328125" style="225" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="225"/>
+    <col min="1" max="1" width="8.7265625" style="224"/>
+    <col min="2" max="2" width="11.6328125" style="224" customWidth="1"/>
+    <col min="3" max="3" width="18.36328125" style="224" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.54296875" style="224" customWidth="1"/>
+    <col min="5" max="5" width="26" style="224" customWidth="1"/>
+    <col min="6" max="6" width="23.90625" style="224" customWidth="1"/>
+    <col min="7" max="8" width="9.36328125" style="224" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="224"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" s="232" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="236" t="s">
+    <row r="1" spans="2:9" s="231" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="B1" s="235" t="s">
         <v>407</v>
       </c>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
-      <c r="H1" s="236"/>
-    </row>
-    <row r="2" spans="2:9" s="231" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="229" t="s">
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+    </row>
+    <row r="2" spans="2:9" s="230" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="228" t="s">
         <v>408</v>
       </c>
-      <c r="C2" s="229" t="s">
+      <c r="C2" s="228" t="s">
         <v>409</v>
       </c>
-      <c r="D2" s="229" t="s">
+      <c r="D2" s="228" t="s">
         <v>410</v>
       </c>
-      <c r="E2" s="229" t="s">
+      <c r="E2" s="228" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="229" t="s">
+      <c r="F2" s="228" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="229" t="s">
+      <c r="G2" s="228" t="s">
         <v>411</v>
       </c>
-      <c r="H2" s="229" t="s">
+      <c r="H2" s="228" t="s">
         <v>412</v>
       </c>
-      <c r="I2" s="230"/>
+      <c r="I2" s="229"/>
     </row>
     <row r="3" spans="2:9" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="147" t="s">
+      <c r="B3" s="146" t="s">
         <v>416</v>
       </c>
-      <c r="C3" s="147" t="s">
+      <c r="C3" s="146" t="s">
         <v>417</v>
       </c>
-      <c r="D3" s="147" t="s">
+      <c r="D3" s="146" t="s">
         <v>418</v>
       </c>
-      <c r="E3" s="160" t="s">
+      <c r="E3" s="159" t="s">
         <v>353</v>
       </c>
-      <c r="F3" s="143" t="s">
+      <c r="F3" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="G3" s="147" t="s">
+      <c r="G3" s="146" t="s">
         <v>419</v>
       </c>
-      <c r="H3" s="147" t="s">
+      <c r="H3" s="146" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="4" spans="2:9" s="227" customFormat="1" ht="81.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="143" t="s">
+    <row r="4" spans="2:9" s="226" customFormat="1" ht="81.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="142" t="s">
         <v>420</v>
       </c>
-      <c r="C4" s="143" t="s">
+      <c r="C4" s="142" t="s">
         <v>424</v>
       </c>
-      <c r="D4" s="160" t="s">
+      <c r="D4" s="159" t="s">
         <v>425</v>
       </c>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="159" t="s">
         <v>363</v>
       </c>
-      <c r="F4" s="228" t="s">
+      <c r="F4" s="227" t="s">
         <v>343</v>
       </c>
-      <c r="G4" s="143" t="s">
+      <c r="G4" s="142" t="s">
         <v>414</v>
       </c>
-      <c r="H4" s="143" t="s">
+      <c r="H4" s="142" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="143" t="s">
+      <c r="B5" s="142" t="s">
         <v>426</v>
       </c>
-      <c r="C5" s="147" t="s">
+      <c r="C5" s="146" t="s">
         <v>427</v>
       </c>
-      <c r="D5" s="147" t="s">
+      <c r="D5" s="146" t="s">
         <v>428</v>
       </c>
-      <c r="E5" s="147" t="s">
+      <c r="E5" s="146" t="s">
         <v>429</v>
       </c>
-      <c r="F5" s="147" t="s">
+      <c r="F5" s="146" t="s">
         <v>291</v>
       </c>
-      <c r="G5" s="147" t="s">
+      <c r="G5" s="146" t="s">
         <v>413</v>
       </c>
-      <c r="H5" s="147" t="s">
+      <c r="H5" s="146" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="B6" s="226"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226" t="s">
+      <c r="B6" s="225"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="225"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="225"/>
+      <c r="G6" s="225" t="s">
         <v>415</v>
       </c>
-      <c r="H6" s="226" t="s">
+      <c r="H6" s="225" t="s">
         <v>415</v>
       </c>
     </row>
@@ -16668,19 +16665,19 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G1:H1 G3:H1048576 G2 I2">
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="LOW">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="VERY HIGH">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="VERY HIGH">
       <formula>NOT(ISERROR(SEARCH("VERY HIGH",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="HIGH">
+    <cfRule type="containsText" dxfId="1" priority="10" operator="containsText" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="VERY HIGH">
+    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="VERY HIGH">
       <formula>NOT(ISERROR(SEARCH("VERY HIGH",G1)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="12" operator="containsText" text="VERY HIGH">
@@ -16699,7 +16696,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83351399-42E2-4271-869A-FE027DEEBD80}">
-  <dimension ref="B1:J28"/>
+  <dimension ref="B1:J27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -16713,573 +16710,563 @@
     <col min="10" max="10" width="6.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+    <row r="1" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="35"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
     </row>
     <row r="2" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
+      <c r="B2" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="36"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
     </row>
     <row r="3" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="153" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
+      <c r="B3" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="37"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
     </row>
     <row r="4" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
+      <c r="B4" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="38"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
       <c r="H4" s="127"/>
       <c r="I4" s="127"/>
     </row>
-    <row r="5" spans="2:10" ht="37" x14ac:dyDescent="0.35">
-      <c r="B5" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="127"/>
-    </row>
-    <row r="7" spans="2:10" ht="41" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="19" t="s">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="126"/>
+    </row>
+    <row r="6" spans="2:10" ht="41" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C6" s="92" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D6" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E6" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F6" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G6" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H6" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I6" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="89" t="s">
+      <c r="J6" s="89" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="109"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="2:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="130"/>
-      <c r="C9" s="93" t="s">
+    <row r="7" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="108"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="2:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="129"/>
+      <c r="C8" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>327</v>
       </c>
+      <c r="E8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="128" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="110"/>
+      <c r="C9" s="94" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>188</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="129" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="128" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="41"/>
+      <c r="J9" s="102" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="111"/>
+    <row r="10" spans="2:10" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="124"/>
       <c r="C10" s="94" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>94</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="129" t="s">
-        <v>125</v>
+        <v>20</v>
+      </c>
+      <c r="G10" s="128" t="s">
+        <v>126</v>
       </c>
       <c r="H10" s="95" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I10" s="41"/>
-      <c r="J10" s="103" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="125"/>
+      <c r="J10" s="102"/>
+    </row>
+    <row r="11" spans="2:10" ht="59" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="109" t="s">
+        <v>88</v>
+      </c>
       <c r="C11" s="94" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="128" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="I11" s="42"/>
+      <c r="J11" s="102" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="109"/>
+      <c r="C12" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="129" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="41"/>
-      <c r="J11" s="103"/>
-    </row>
-    <row r="12" spans="2:10" ht="59" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="110" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="94" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="129" t="s">
-        <v>122</v>
+      <c r="F12" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="128" t="s">
+        <v>157</v>
       </c>
       <c r="H12" s="41" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I12" s="42"/>
-      <c r="J12" s="103" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="110"/>
+      <c r="J12" s="102"/>
+    </row>
+    <row r="13" spans="2:10" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="109"/>
       <c r="C13" s="94" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>94</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="129" t="s">
-        <v>157</v>
+        <v>128</v>
+      </c>
+      <c r="G13" s="128" t="s">
+        <v>129</v>
       </c>
       <c r="H13" s="41" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I13" s="42"/>
-      <c r="J13" s="103"/>
+      <c r="J13" s="102"/>
     </row>
     <row r="14" spans="2:10" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="110"/>
-      <c r="C14" s="94" t="s">
-        <v>165</v>
+      <c r="B14" s="109"/>
+      <c r="C14" s="96" t="s">
+        <v>166</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="G14" s="129" t="s">
-        <v>129</v>
-      </c>
-      <c r="H14" s="41" t="s">
-        <v>130</v>
+        <v>152</v>
+      </c>
+      <c r="F14" s="107" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="128" t="s">
+        <v>155</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>153</v>
       </c>
       <c r="I14" s="42"/>
-      <c r="J14" s="103"/>
-    </row>
-    <row r="15" spans="2:10" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J14" s="102"/>
+    </row>
+    <row r="15" spans="2:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="110"/>
       <c r="C15" s="96" t="s">
-        <v>166</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>158</v>
+        <v>167</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F15" s="108" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="129" t="s">
-        <v>155</v>
+        <v>94</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="128" t="s">
+        <v>124</v>
       </c>
       <c r="H15" s="42" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="I15" s="42"/>
-      <c r="J15" s="103"/>
-    </row>
-    <row r="16" spans="2:10" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="111"/>
+      <c r="J15" s="102"/>
+    </row>
+    <row r="16" spans="2:10" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="130"/>
       <c r="C16" s="96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>94</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="129" t="s">
-        <v>124</v>
+        <v>66</v>
+      </c>
+      <c r="G16" s="128" t="s">
+        <v>156</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="I16" s="42"/>
-      <c r="J16" s="103"/>
-    </row>
-    <row r="17" spans="2:10" ht="86.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="131"/>
-      <c r="C17" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" s="129" t="s">
-        <v>156</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>67</v>
-      </c>
+      <c r="J16" s="102"/>
+    </row>
+    <row r="17" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="108"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
       <c r="I17" s="42"/>
-      <c r="J17" s="103"/>
-    </row>
-    <row r="18" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="109"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="J17" s="102"/>
+    </row>
+    <row r="18" spans="2:10" ht="101" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="131"/>
+      <c r="C18" s="93" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="116" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>28</v>
+      </c>
       <c r="I18" s="42"/>
-      <c r="J18" s="103"/>
-    </row>
-    <row r="19" spans="2:10" ht="101" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="132"/>
-      <c r="C19" s="93" t="s">
-        <v>169</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>33</v>
+      <c r="J18" s="102"/>
+    </row>
+    <row r="19" spans="2:10" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="111"/>
+      <c r="C19" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>31</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="41" t="s">
-        <v>27</v>
+      <c r="F19" s="43" t="s">
+        <v>32</v>
       </c>
       <c r="G19" s="117" t="s">
-        <v>138</v>
-      </c>
-      <c r="H19" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="42"/>
-      <c r="J19" s="103"/>
-    </row>
-    <row r="20" spans="2:10" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="112"/>
+        <v>139</v>
+      </c>
+      <c r="H19" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="48"/>
+      <c r="J19" s="102"/>
+    </row>
+    <row r="20" spans="2:10" ht="117" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="112" t="s">
+        <v>120</v>
+      </c>
       <c r="C20" s="94" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="118" t="s">
-        <v>139</v>
+        <v>36</v>
+      </c>
+      <c r="G20" s="117" t="s">
+        <v>136</v>
       </c>
       <c r="H20" s="48" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I20" s="48"/>
-      <c r="J20" s="103"/>
-    </row>
-    <row r="21" spans="2:10" ht="117" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="113" t="s">
-        <v>120</v>
-      </c>
+      <c r="J20" s="102"/>
+    </row>
+    <row r="21" spans="2:10" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="111"/>
       <c r="C21" s="94" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F21" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="118" t="s">
-        <v>136</v>
+        <v>39</v>
+      </c>
+      <c r="G21" s="117" t="s">
+        <v>137</v>
       </c>
       <c r="H21" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="I21" s="48"/>
-      <c r="J21" s="103"/>
-    </row>
-    <row r="22" spans="2:10" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="112"/>
-      <c r="C22" s="94" t="s">
-        <v>172</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="I21" s="121"/>
+      <c r="J21" s="102"/>
+    </row>
+    <row r="22" spans="2:10" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="111"/>
+      <c r="C22" s="96" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>48</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="118" t="s">
-        <v>137</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="122"/>
-      <c r="J22" s="103"/>
-    </row>
-    <row r="23" spans="2:10" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="112"/>
+      <c r="F22" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="116" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="44"/>
+      <c r="J22" s="102"/>
+    </row>
+    <row r="23" spans="2:10" ht="123" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="111"/>
       <c r="C23" s="96" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="117" t="s">
-        <v>138</v>
-      </c>
-      <c r="H23" s="121" t="s">
-        <v>50</v>
+        <v>141</v>
+      </c>
+      <c r="G23" s="116" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="120" t="s">
+        <v>53</v>
       </c>
       <c r="I23" s="44"/>
-      <c r="J23" s="103"/>
-    </row>
-    <row r="24" spans="2:10" ht="123" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="112"/>
+      <c r="J23" s="102"/>
+    </row>
+    <row r="24" spans="2:10" ht="107" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="132"/>
       <c r="C24" s="96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>142</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="G24" s="117" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="121" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="44"/>
-      <c r="J24" s="103"/>
-    </row>
-    <row r="25" spans="2:10" ht="107" customHeight="1" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+      <c r="G24" s="116" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="97" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="122"/>
+      <c r="J24" s="102"/>
+    </row>
+    <row r="25" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B25" s="133"/>
-      <c r="C25" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="117" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="97" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25" s="123"/>
-      <c r="J25" s="103"/>
-    </row>
-    <row r="26" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B26" s="134"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="52"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="102"/>
+    </row>
+    <row r="26" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="119"/>
+      <c r="C26" s="93" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="52" t="s">
+        <v>60</v>
+      </c>
       <c r="I26" s="46"/>
-      <c r="J26" s="103"/>
-    </row>
-    <row r="27" spans="2:10" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="120"/>
+      <c r="J26" s="102"/>
+    </row>
+    <row r="27" spans="2:10" ht="86" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="118" t="s">
+        <v>121</v>
+      </c>
       <c r="C27" s="93" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F27" s="46" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G27" s="46" t="s">
         <v>144</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="46"/>
-      <c r="J27" s="103"/>
-    </row>
-    <row r="28" spans="2:10" ht="86" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119" t="s">
-        <v>121</v>
-      </c>
-      <c r="C28" s="93" t="s">
-        <v>177</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F28" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="I28" s="124"/>
-      <c r="J28" s="103"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="102"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J9:J28" xr:uid="{A43EC6DC-F9AC-4243-BA3C-D0330B5CA670}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8:J27" xr:uid="{A43EC6DC-F9AC-4243-BA3C-D0330B5CA670}">
       <formula1>"PASS,FAIL,ON HOLD"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17310,7 +17297,7 @@
       <c r="B1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="233"/>
+      <c r="C1" s="232"/>
       <c r="D1" s="16"/>
     </row>
     <row r="2" spans="1:4" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
